--- a/docs/community-docmentation-review.xlsx
+++ b/docs/community-docmentation-review.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cassandragouldvanpraag/Library/Mobile Documents/com~apple~CloudDocs/repos/rcmcooperative/partner-UKTRE/community-management/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B362693E-DC19-314F-91C6-485042F0810F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E662AA4-72E0-CC46-9226-EA96ABFBE152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="1500" windowWidth="27640" windowHeight="15380" xr2:uid="{617020EF-C870-DD41-BC87-7763A01FCE3E}"/>
+    <workbookView xWindow="0" yWindow="1060" windowWidth="30560" windowHeight="17220" activeTab="1" xr2:uid="{617020EF-C870-DD41-BC87-7763A01FCE3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$E$5:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
   <si>
     <t>Competency</t>
   </si>
@@ -168,18 +173,78 @@
   </si>
   <si>
     <t>Papers</t>
+  </si>
+  <si>
+    <t>Communication and Engagement Total</t>
+  </si>
+  <si>
+    <t>Strategic Contributions Total</t>
+  </si>
+  <si>
+    <t>Technical Expertise Total</t>
+  </si>
+  <si>
+    <t>Accountability Total</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Communication and Engagement Count</t>
+  </si>
+  <si>
+    <t>Strategic Contributions Count</t>
+  </si>
+  <si>
+    <t>Technical Expertise Count</t>
+  </si>
+  <si>
+    <t>Accountability Count</t>
+  </si>
+  <si>
+    <t>Grand Count</t>
+  </si>
+  <si>
+    <t>Count total</t>
+  </si>
+  <si>
+    <t>% complete</t>
+  </si>
+  <si>
+    <t>total %</t>
+  </si>
+  <si>
+    <t>remainder</t>
+  </si>
+  <si>
+    <t>complete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -203,9 +268,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -221,6 +290,3519 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:t>Communication and Engagement</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.21430555555555558"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Communication and Engagement</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="31750">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0627-2943-B52B-0C623CE770EF}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-0627-2943-B52B-0C623CE770EF}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.44583333333333336</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5541666666666667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0627-2943-B52B-0C623CE770EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="52"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:t>Technical expertise</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.31708333333333333"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Technical Expertise Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A90B-004E-B319-CEFC3B50A9FA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-A90B-004E-B319-CEFC3B50A9FA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$20:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.35749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64250000000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A90B-004E-B319-CEFC3B50A9FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="52"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:t>Accountability</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35597222222222225"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Accountability Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D94A-DA44-9E91-316F80D7DB11}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D94A-DA44-9E91-316F80D7DB11}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.38900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.61099999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-D94A-DA44-9E91-316F80D7DB11}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="52"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:t>Strategic contributions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.28930555555555554"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Strategic Contributions Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1949-3F40-9B9E-BEF255FFFBAA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1949-3F40-9B9E-BEF255FFFBAA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$21:$G$21</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86099999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1949-3F40-9B9E-BEF255FFFBAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="52"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>314960</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>86360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>772160</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>187960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE1E762F-9791-8FE3-F437-E6091A523341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D9F407F-6DFE-9B4C-9D5D-3126CD294567}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>314960</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>467360</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>162560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3198B0AE-B3A1-924F-B5E2-37F6B0493B23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCAB7E5D-CC51-4D44-A986-060E57793EDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.39111</cdr:x>
+      <cdr:y>0.43148</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.63111</cdr:x>
+      <cdr:y>0.66852</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="Sheet2!$F$18">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B14FF4E-8434-654A-E5F4-1D57CCDD68FC}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1788160" y="1183640"/>
+          <a:ext cx="1097280" cy="650240"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fld id="{8E4BD7CC-552D-E247-844D-D380A79B85B0}" type="TxLink">
+            <a:rPr lang="en-US" sz="4000" b="1" i="0" u="none" strike="noStrike" kern="1200">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t>45%</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="4000" b="1" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.39111</cdr:x>
+      <cdr:y>0.43148</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.63111</cdr:x>
+      <cdr:y>0.66852</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="Sheet2!$F$20">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B14FF4E-8434-654A-E5F4-1D57CCDD68FC}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1788160" y="1183640"/>
+          <a:ext cx="1097280" cy="650240"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fld id="{972DC064-193E-2645-9A11-DBAA95347CE3}" type="TxLink">
+            <a:rPr lang="en-US" sz="4000" b="1" i="0" u="none" strike="noStrike" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t>36%</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="4000" b="1" kern="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.39111</cdr:x>
+      <cdr:y>0.43148</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.63111</cdr:x>
+      <cdr:y>0.66852</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="Sheet2!$F$19">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B14FF4E-8434-654A-E5F4-1D57CCDD68FC}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1788160" y="1183640"/>
+          <a:ext cx="1097280" cy="650240"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fld id="{099C582B-D91A-7849-B2EE-390B43A33A13}" type="TxLink">
+            <a:rPr lang="en-US" sz="4000" b="1" i="0" u="none" strike="noStrike" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t>39%</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="4000" b="1" kern="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.39111</cdr:x>
+      <cdr:y>0.43148</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.63111</cdr:x>
+      <cdr:y>0.66852</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="Sheet2!$F$21">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B14FF4E-8434-654A-E5F4-1D57CCDD68FC}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1788160" y="1183640"/>
+          <a:ext cx="1097280" cy="650240"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fld id="{32124D48-BAE0-4F4E-ABBE-24654EF18AF8}" type="TxLink">
+            <a:rPr lang="en-US" sz="4000" b="1" i="0" u="none" strike="noStrike" kern="1200">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t>14%</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="4000" b="1" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -540,21 +4122,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C411906-826C-944B-8CFB-0EB298C69588}">
-  <dimension ref="B2:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:D52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="3" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -565,7 +4152,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -576,7 +4163,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -587,7 +4174,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -598,7 +4185,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -609,7 +4196,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>3</v>
       </c>
@@ -620,7 +4207,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>3</v>
       </c>
@@ -631,7 +4218,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -642,7 +4229,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>3</v>
       </c>
@@ -653,7 +4240,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>3</v>
       </c>
@@ -664,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>3</v>
       </c>
@@ -675,7 +4262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>3</v>
       </c>
@@ -686,315 +4273,585 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
+    <row r="15" spans="2:4" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="4">
+        <f>SUBTOTAL(3,D3:D14)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D16" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+        <f>SUBTOTAL(9,D3:D14)</f>
+        <v>5.3500000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D26" s="1">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" t="s">
-        <v>30</v>
+    <row r="27" spans="2:4" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="4">
+        <f>SUBTOTAL(3,D17:D26)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="D28" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+        <f>SUBTOTAL(9,D17:D26)</f>
+        <v>1.3900000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>26</v>
       </c>
       <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D36" s="1">
         <v>0.36</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" t="s">
-        <v>40</v>
+    <row r="37" spans="2:4" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="4">
+        <f>SUBTOTAL(3,D29:D36)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+        <f>SUBTOTAL(9,D29:D36)</f>
+        <v>2.8600000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>34</v>
       </c>
       <c r="C42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D48" s="1">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="4">
+        <f>SUBTOTAL(3,D39:D48)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="1">
+        <f>SUBTOTAL(9,D39:D48)</f>
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="4">
+        <f>SUBTOTAL(3,D3:D48)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="1">
+        <f>SUBTOTAL(9,D3:D48)</f>
+        <v>13.489999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:D48" xr:uid="{3C411906-826C-944B-8CFB-0EB298C69588}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9A3704-0B3D-4E4B-8296-9205471A3217}">
+  <dimension ref="E5:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="36.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="5">
+        <v>535</v>
+      </c>
+      <c r="G6">
+        <v>1200</v>
+      </c>
+      <c r="H6" s="1">
+        <f>F6/G6</f>
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <f>I6-H6</f>
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="5">
+        <v>389</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" ref="H7" si="0">F7/G7</f>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" ref="J7:J9" si="1">I7-H7</f>
+        <v>0.61099999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="5">
+        <v>286</v>
+      </c>
+      <c r="G8">
+        <v>800</v>
+      </c>
+      <c r="H8" s="1">
+        <f>F8/G8</f>
+        <v>0.35749999999999998</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+        <v>0.64250000000000007</v>
+      </c>
+    </row>
+    <row r="9" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="5">
+        <v>139</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9" s="1">
+        <f>F9/G9</f>
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+        <v>0.86099999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.5541666666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.61099999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.35749999999999998</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.64250000000000007</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.86099999999999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>